--- a/CutlistTestSheet_Cutlist_.xlsx
+++ b/CutlistTestSheet_Cutlist_.xlsx
@@ -31,6 +31,9 @@
     <x:t>P1-a5</x:t>
   </x:si>
   <x:si>
+    <x:t>Duplicate Part Numbers with identical properties</x:t>
+  </x:si>
+  <x:si>
     <x:t>P1-a10</x:t>
   </x:si>
   <x:si>
@@ -46,18 +49,27 @@
     <x:t>P1-a7</x:t>
   </x:si>
   <x:si>
+    <x:t>P1-a9</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Duplicate Part Number with Different Length</x:t>
+  </x:si>
+  <x:si>
     <x:t>P1-a8</x:t>
   </x:si>
   <x:si>
-    <x:t>P1-a9</x:t>
+    <x:t>P1-a11</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Duplicate Part Number with Different Material</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Stick 3</x:t>
   </x:si>
   <x:si>
     <x:t>P1-a2</x:t>
   </x:si>
   <x:si>
-    <x:t>P1-a11</x:t>
-  </x:si>
-  <x:si>
     <x:t>L6x6x1/4</x:t>
   </x:si>
   <x:si>
@@ -68,6 +80,9 @@
   </x:si>
   <x:si>
     <x:t>test2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HSS3X3X1/8</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -77,7 +92,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="0" formatCode=""/>
   </x:numFmts>
-  <x:fonts count="2">
+  <x:fonts count="4">
     <x:font>
       <x:vertAlign val="baseline"/>
       <x:sz val="11"/>
@@ -93,8 +108,23 @@
       <x:name val="Calibri"/>
       <x:family val="2"/>
     </x:font>
+    <x:font>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFF0000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:vertAlign val="baseline"/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFF0000"/>
+      <x:name val="Calibri"/>
+      <x:family val="2"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="3">
+  <x:fills count="5">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -106,6 +136,16 @@
         <x:fgColor rgb="FFD3D3D3"/>
       </x:patternFill>
     </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFE0"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFF00"/>
+      </x:patternFill>
+    </x:fill>
   </x:fills>
   <x:borders count="2">
     <x:border diagonalUp="0" diagonalDown="0">
@@ -143,7 +183,7 @@
       </x:diagonal>
     </x:border>
   </x:borders>
-  <x:cellStyleXfs count="3">
+  <x:cellStyleXfs count="7">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -153,8 +193,20 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <x:protection locked="1" hidden="0"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
   </x:cellStyleXfs>
-  <x:cellXfs count="3">
+  <x:cellXfs count="7">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
@@ -164,6 +216,22 @@
       <x:protection locked="1" hidden="0"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <x:protection locked="1" hidden="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="1">
       <x:alignment horizontal="general" vertical="center" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <x:protection locked="1" hidden="0"/>
     </x:xf>
@@ -462,14 +530,16 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:B40"/>
+  <x:dimension ref="A1:Z47"/>
   <x:sheetFormatPr defaultRowHeight="20" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="12.424911" style="0" customWidth="1"/>
     <x:col min="2" max="2" width="7.853482" style="0" customWidth="1"/>
+    <x:col min="3" max="3" width="44.567768" style="0" customWidth="1"/>
+    <x:col min="4" max="26" width="9.140625" style="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:2">
+    <x:row r="1" spans="1:26">
       <x:c r="A1" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -477,7 +547,7 @@
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:2">
+    <x:row r="2" spans="1:26">
       <x:c r="A2" s="2" t="s">
         <x:v>2</x:v>
       </x:c>
@@ -485,7 +555,7 @@
         <x:v>82</x:v>
       </x:c>
     </x:row>
-    <x:row r="3" spans="1:2">
+    <x:row r="3" spans="1:26">
       <x:c r="A3" s="2" t="s">
         <x:v>3</x:v>
       </x:c>
@@ -493,268 +563,326 @@
         <x:v>80</x:v>
       </x:c>
     </x:row>
-    <x:row r="4" spans="1:2">
-      <x:c r="A4" s="2" t="s">
+    <x:row r="4" spans="1:26">
+      <x:c r="A4" s="3" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B4" s="2">
+      <x:c r="B4" s="3">
         <x:v>53.375</x:v>
       </x:c>
-    </x:row>
-    <x:row r="5" spans="1:2">
+      <x:c r="C4" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:26">
       <x:c r="A5" s="2" t="s">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="B5" s="2">
         <x:v>12.8125</x:v>
       </x:c>
     </x:row>
-    <x:row r="6" spans="1:2">
+    <x:row r="6" spans="1:26">
       <x:c r="A6" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B6" s="2">
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="7" spans="1:2">
+    <x:row r="7" spans="1:26">
       <x:c r="A7" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B7" s="2">
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:2">
+    <x:row r="9" spans="1:26">
       <x:c r="A9" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:2">
-      <x:c r="A10" s="2" t="s">
         <x:v>8</x:v>
       </x:c>
-      <x:c r="B10" s="2">
-        <x:v>47.1875</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:2">
+    </x:row>
+    <x:row r="10" spans="1:26">
+      <x:c r="A10" s="3" t="s">
+        <x:v>4</x:v>
+      </x:c>
+      <x:c r="B10" s="3">
+        <x:v>53.375</x:v>
+      </x:c>
+      <x:c r="C10" s="4" t="s">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:26">
       <x:c r="A11" s="2" t="s">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B11" s="2">
-        <x:v>33.25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:2">
+        <x:v>47.1875</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:26">
       <x:c r="A12" s="2" t="s">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B12" s="2">
+        <x:v>33.25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:26">
+      <x:c r="A13" s="5" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B13" s="5">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C13" s="6" t="s">
+        <x:v>12</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:26">
+      <x:c r="A14" s="2" t="s">
+        <x:v>13</x:v>
+      </x:c>
+      <x:c r="B14" s="2">
         <x:v>30.4375</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:2">
-      <x:c r="A13" s="2" t="s">
+    <x:row r="15" spans="1:26">
+      <x:c r="A15" s="5" t="s">
         <x:v>11</x:v>
       </x:c>
-      <x:c r="B13" s="2">
+      <x:c r="B15" s="5">
         <x:v>28.4375</x:v>
       </x:c>
-    </x:row>
-    <x:row r="14" spans="1:2">
-      <x:c r="A14" s="2" t="s">
+      <x:c r="C15" s="6" t="s">
         <x:v>12</x:v>
       </x:c>
-      <x:c r="B14" s="2">
+    </x:row>
+    <x:row r="16" spans="1:26">
+      <x:c r="A16" s="5" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B16" s="5">
+        <x:v>11.4375</x:v>
+      </x:c>
+      <x:c r="C16" s="6" t="s">
+        <x:v>15</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:26">
+      <x:c r="A18" s="1" t="s">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="B18" s="1" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:26">
+      <x:c r="A19" s="2" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B19" s="2">
         <x:v>24.4375</x:v>
       </x:c>
     </x:row>
-    <x:row r="15" spans="1:2">
-      <x:c r="A15" s="2" t="s">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="B15" s="2">
+    <x:row r="20" spans="1:26">
+      <x:c r="A20" s="2" t="s">
+        <x:v>17</x:v>
+      </x:c>
+      <x:c r="B20" s="2">
         <x:v>24.4375</x:v>
       </x:c>
     </x:row>
-    <x:row r="16" spans="1:2">
-      <x:c r="A16" s="2" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="B16" s="2">
-        <x:v>11.4375</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:2">
-      <x:c r="A17" s="2" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B17" s="2">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:2">
-      <x:c r="A18" s="2" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B18" s="2">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:2">
-      <x:c r="A19" s="2" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B19" s="2">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:2">
-      <x:c r="A20" s="2" t="s">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="B20" s="2">
-        <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:2">
+    <x:row r="21" spans="1:26">
       <x:c r="A21" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B21" s="2">
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="22" spans="1:2">
+    <x:row r="22" spans="1:26">
       <x:c r="A22" s="2" t="s">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B22" s="2">
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" spans="1:2">
-      <x:c r="A24" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B24" s="1" t="s">
-        <x:v>1</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:2">
+    <x:row r="23" spans="1:26">
+      <x:c r="A23" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B23" s="2">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:26">
+      <x:c r="A24" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B24" s="2">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:26">
       <x:c r="A25" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B25" s="2">
-        <x:v>20.6875</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:2">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:26">
       <x:c r="A26" s="2" t="s">
-        <x:v>15</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="B26" s="2">
-        <x:v>20.6875</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:2">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:26">
       <x:c r="A28" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" spans="1:2">
+    <x:row r="29" spans="1:26">
       <x:c r="A29" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B29" s="2">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:2">
+        <x:v>20.6875</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:26">
       <x:c r="A30" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="B30" s="2">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:2">
-      <x:c r="A31" s="2" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B31" s="2">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:2">
-      <x:c r="A32" s="2" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B32" s="2">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:2">
+        <x:v>20.6875</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:26">
+      <x:c r="A32" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B32" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:26">
       <x:c r="A33" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B33" s="2">
         <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="34" spans="1:2">
+    <x:row r="34" spans="1:26">
       <x:c r="A34" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B34" s="2">
         <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="35" spans="1:2">
+    <x:row r="35" spans="1:26">
       <x:c r="A35" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B35" s="2">
         <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="36" spans="1:2">
+    <x:row r="36" spans="1:26">
       <x:c r="A36" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B36" s="2">
         <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="38" spans="1:2">
-      <x:c r="A38" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="B38" s="1" t="s">
-        <x:v>7</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:2">
+    <x:row r="37" spans="1:26">
+      <x:c r="A37" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B37" s="2">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:26">
+      <x:c r="A38" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B38" s="2">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:26">
       <x:c r="A39" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B39" s="2">
         <x:v>32</x:v>
       </x:c>
     </x:row>
-    <x:row r="40" spans="1:2">
+    <x:row r="40" spans="1:26">
       <x:c r="A40" s="2" t="s">
-        <x:v>17</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="B40" s="2">
         <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:26">
+      <x:c r="A42" s="1" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B42" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:26">
+      <x:c r="A43" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B43" s="2">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:26">
+      <x:c r="A44" s="2" t="s">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="B44" s="2">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:26">
+      <x:c r="A46" s="1" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B46" s="1" t="s">
+        <x:v>1</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:26">
+      <x:c r="A47" s="5" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B47" s="5">
+        <x:v>11.4375</x:v>
+      </x:c>
+      <x:c r="C47" s="6" t="s">
+        <x:v>15</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -763,7 +891,7 @@
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed" verticalDpi="300"/>
   <x:headerFooter/>
   <x:rowBreaks count="1" manualBreakCount="1">
-    <x:brk id="27" max="1048576" man="1"/>
+    <x:brk id="31" max="1048576" man="1"/>
   </x:rowBreaks>
   <x:tableParts count="0"/>
 </x:worksheet>

--- a/CutlistTestSheet_Cutlist_.xlsx
+++ b/CutlistTestSheet_Cutlist_.xlsx
@@ -38,6 +38,9 @@
   </x:si>
   <x:si>
     <x:t>Ca1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Drop(in):</x:t>
   </x:si>
   <x:si>
     <x:t>Stick 2</x:t>
@@ -530,7 +533,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:Z47"/>
+  <x:dimension ref="A1:Z54"/>
   <x:sheetFormatPr defaultRowHeight="20" customHeight="1"/>
   <x:cols>
     <x:col min="1" max="1" width="12.424911" style="0" customWidth="1"/>
@@ -598,31 +601,31 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
-    <x:row r="9" spans="1:26">
-      <x:c r="A9" s="1" t="s">
+    <x:row r="8" spans="1:26">
+      <x:c r="A8" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B8" s="1">
+        <x:v>0.6875</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:26">
+      <x:c r="A10" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B9" s="1" t="s">
-        <x:v>8</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:26">
-      <x:c r="A10" s="3" t="s">
+      <x:c r="B10" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:26">
+      <x:c r="A11" s="3" t="s">
         <x:v>4</x:v>
       </x:c>
-      <x:c r="B10" s="3">
+      <x:c r="B11" s="3">
         <x:v>53.375</x:v>
       </x:c>
-      <x:c r="C10" s="4" t="s">
+      <x:c r="C11" s="4" t="s">
         <x:v>5</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:26">
-      <x:c r="A11" s="2" t="s">
-        <x:v>9</x:v>
-      </x:c>
-      <x:c r="B11" s="2">
-        <x:v>47.1875</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:26">
@@ -630,88 +633,88 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="B12" s="2">
+        <x:v>47.1875</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:26">
+      <x:c r="A13" s="2" t="s">
+        <x:v>11</x:v>
+      </x:c>
+      <x:c r="B13" s="2">
         <x:v>33.25</x:v>
       </x:c>
     </x:row>
-    <x:row r="13" spans="1:26">
-      <x:c r="A13" s="5" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B13" s="5">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="C13" s="6" t="s">
+    <x:row r="14" spans="1:26">
+      <x:c r="A14" s="5" t="s">
         <x:v>12</x:v>
       </x:c>
-    </x:row>
-    <x:row r="14" spans="1:26">
-      <x:c r="A14" s="2" t="s">
+      <x:c r="B14" s="5">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="C14" s="6" t="s">
         <x:v>13</x:v>
       </x:c>
-      <x:c r="B14" s="2">
+    </x:row>
+    <x:row r="15" spans="1:26">
+      <x:c r="A15" s="2" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="B15" s="2">
         <x:v>30.4375</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:26">
-      <x:c r="A15" s="5" t="s">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="B15" s="5">
-        <x:v>28.4375</x:v>
-      </x:c>
-      <x:c r="C15" s="6" t="s">
-        <x:v>12</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:26">
       <x:c r="A16" s="5" t="s">
-        <x:v>14</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="B16" s="5">
+        <x:v>28.4375</x:v>
+      </x:c>
+      <x:c r="C16" s="6" t="s">
+        <x:v>13</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:26">
+      <x:c r="A17" s="5" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B17" s="5">
         <x:v>11.4375</x:v>
       </x:c>
-      <x:c r="C16" s="6" t="s">
-        <x:v>15</x:v>
+      <x:c r="C17" s="6" t="s">
+        <x:v>16</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:26">
       <x:c r="A18" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B18" s="1">
+        <x:v>2.5625</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:26">
+      <x:c r="A20" s="1" t="s">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="B18" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:26">
-      <x:c r="A19" s="2" t="s">
+      <x:c r="B20" s="1" t="s">
         <x:v>17</x:v>
-      </x:c>
-      <x:c r="B19" s="2">
-        <x:v>24.4375</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:26">
-      <x:c r="A20" s="2" t="s">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="B20" s="2">
-        <x:v>24.4375</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:26">
       <x:c r="A21" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B21" s="2">
-        <x:v>5</x:v>
+        <x:v>24.4375</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:26">
       <x:c r="A22" s="2" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B22" s="2">
-        <x:v>5</x:v>
+        <x:v>24.4375</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:26">
@@ -746,73 +749,73 @@
         <x:v>5</x:v>
       </x:c>
     </x:row>
+    <x:row r="27" spans="1:26">
+      <x:c r="A27" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B27" s="2">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
     <x:row r="28" spans="1:26">
-      <x:c r="A28" s="1" t="s">
-        <x:v>18</x:v>
-      </x:c>
-      <x:c r="B28" s="1" t="s">
+      <x:c r="A28" s="2" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="B28" s="2">
+        <x:v>5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:26">
+      <x:c r="A29" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B29" s="1">
+        <x:v>159.625</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:26">
+      <x:c r="A31" s="1" t="s">
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="B31" s="1" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="29" spans="1:26">
-      <x:c r="A29" s="2" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B29" s="2">
+    <x:row r="32" spans="1:26">
+      <x:c r="A32" s="2" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B32" s="2">
         <x:v>20.6875</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:26">
-      <x:c r="A30" s="2" t="s">
-        <x:v>19</x:v>
-      </x:c>
-      <x:c r="B30" s="2">
-        <x:v>20.6875</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:26">
-      <x:c r="A32" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B32" s="1" t="s">
-        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:26">
       <x:c r="A33" s="2" t="s">
+        <x:v>20</x:v>
+      </x:c>
+      <x:c r="B33" s="2">
+        <x:v>20.6875</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:26">
+      <x:c r="A34" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B34" s="1">
+        <x:v>246.25</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:26">
+      <x:c r="A36" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B33" s="2">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:26">
-      <x:c r="A34" s="2" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B34" s="2">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:26">
-      <x:c r="A35" s="2" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B35" s="2">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:26">
-      <x:c r="A36" s="2" t="s">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="B36" s="2">
-        <x:v>32</x:v>
+      <x:c r="B36" s="1" t="s">
+        <x:v>1</x:v>
       </x:c>
     </x:row>
     <x:row r="37" spans="1:26">
       <x:c r="A37" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B37" s="2">
         <x:v>32</x:v>
@@ -820,7 +823,7 @@
     </x:row>
     <x:row r="38" spans="1:26">
       <x:c r="A38" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B38" s="2">
         <x:v>32</x:v>
@@ -828,7 +831,7 @@
     </x:row>
     <x:row r="39" spans="1:26">
       <x:c r="A39" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B39" s="2">
         <x:v>32</x:v>
@@ -836,23 +839,31 @@
     </x:row>
     <x:row r="40" spans="1:26">
       <x:c r="A40" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B40" s="2">
         <x:v>32</x:v>
       </x:c>
     </x:row>
+    <x:row r="41" spans="1:26">
+      <x:c r="A41" s="2" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B41" s="2">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
     <x:row r="42" spans="1:26">
-      <x:c r="A42" s="1" t="s">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="B42" s="1" t="s">
-        <x:v>8</x:v>
+      <x:c r="A42" s="2" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B42" s="2">
+        <x:v>32</x:v>
       </x:c>
     </x:row>
     <x:row r="43" spans="1:26">
       <x:c r="A43" s="2" t="s">
-        <x:v>21</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="B43" s="2">
         <x:v>32</x:v>
@@ -860,29 +871,77 @@
     </x:row>
     <x:row r="44" spans="1:26">
       <x:c r="A44" s="2" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B44" s="2">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:26">
+      <x:c r="A45" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B45" s="1">
+        <x:v>30.5</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:26">
+      <x:c r="A47" s="1" t="s">
         <x:v>21</x:v>
       </x:c>
-      <x:c r="B44" s="2">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:26">
-      <x:c r="A46" s="1" t="s">
+      <x:c r="B47" s="1" t="s">
+        <x:v>9</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:26">
+      <x:c r="A48" s="2" t="s">
         <x:v>22</x:v>
       </x:c>
-      <x:c r="B46" s="1" t="s">
+      <x:c r="B48" s="2">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:26">
+      <x:c r="A49" s="2" t="s">
+        <x:v>22</x:v>
+      </x:c>
+      <x:c r="B49" s="2">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:26">
+      <x:c r="A50" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B50" s="1">
+        <x:v>223.625</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:26">
+      <x:c r="A52" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="B52" s="1" t="s">
         <x:v>1</x:v>
       </x:c>
     </x:row>
-    <x:row r="47" spans="1:26">
-      <x:c r="A47" s="5" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="B47" s="5">
+    <x:row r="53" spans="1:26">
+      <x:c r="A53" s="5" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="B53" s="5">
         <x:v>11.4375</x:v>
       </x:c>
-      <x:c r="C47" s="6" t="s">
-        <x:v>15</x:v>
+      <x:c r="C53" s="6" t="s">
+        <x:v>16</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:26">
+      <x:c r="A54" s="1" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="B54" s="1">
+        <x:v>228.375</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -891,7 +950,7 @@
   <x:pageSetup paperSize="1" scale="100" pageOrder="downThenOver" orientation="default" blackAndWhite="0" draft="0" cellComments="none" errors="displayed" verticalDpi="300"/>
   <x:headerFooter/>
   <x:rowBreaks count="1" manualBreakCount="1">
-    <x:brk id="31" max="1048576" man="1"/>
+    <x:brk id="35" max="1048576" man="1"/>
   </x:rowBreaks>
   <x:tableParts count="0"/>
 </x:worksheet>
